--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N120_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N120_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.30915735327958</v>
+        <v>1.675238069907932</v>
       </c>
       <c r="D2" t="n">
-        <v>68.44443122575311</v>
+        <v>11.12222007418488</v>
       </c>
       <c r="E2" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F2" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.57737973711325</v>
+        <v>2.368824207280903</v>
       </c>
       <c r="D3" t="n">
-        <v>35.70681303241547</v>
+        <v>5.802357117767514</v>
       </c>
       <c r="E3" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F3" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.52126697267815</v>
+        <v>3.8222058830602</v>
       </c>
       <c r="D4" t="n">
-        <v>30.39853286737514</v>
+        <v>4.93976159094846</v>
       </c>
       <c r="E4" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F4" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.35353276558002</v>
+        <v>2.007449074406753</v>
       </c>
       <c r="D5" t="n">
-        <v>45.22634080372953</v>
+        <v>7.349280380606048</v>
       </c>
       <c r="E5" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F5" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.34783942384322</v>
+        <v>4.606523906374522</v>
       </c>
       <c r="D6" t="n">
-        <v>27.52467072462537</v>
+        <v>4.472758992751623</v>
       </c>
       <c r="E6" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F6" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.14524233062049</v>
+        <v>4.73610187872583</v>
       </c>
       <c r="D7" t="n">
-        <v>55.38967305130249</v>
+        <v>9.000821870836656</v>
       </c>
       <c r="E7" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F7" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.14903329502104</v>
+        <v>3.761717910440919</v>
       </c>
       <c r="D8" t="n">
-        <v>18.33208228552104</v>
+        <v>2.978963371397169</v>
       </c>
       <c r="E8" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F8" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.20170657164149</v>
+        <v>2.957777317891743</v>
       </c>
       <c r="D9" t="n">
-        <v>62.64004430543005</v>
+        <v>10.17900719963238</v>
       </c>
       <c r="E9" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F9" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.19262697736837</v>
+        <v>4.25630188382236</v>
       </c>
       <c r="D10" t="n">
-        <v>26.41940162137455</v>
+        <v>4.293152763473364</v>
       </c>
       <c r="E10" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F10" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>10.57567096708696</v>
+        <v>1.71854653215163</v>
       </c>
       <c r="D11" t="n">
-        <v>21.09671271224217</v>
+        <v>3.428215815739352</v>
       </c>
       <c r="E11" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F11" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.41284297843738</v>
+        <v>2.829586983996075</v>
       </c>
       <c r="D12" t="n">
-        <v>32.54232404059044</v>
+        <v>5.288127656595948</v>
       </c>
       <c r="E12" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F12" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>18.70725058606412</v>
+        <v>3.039928220235419</v>
       </c>
       <c r="D13" t="n">
-        <v>30.86256206301443</v>
+        <v>5.015166335239845</v>
       </c>
       <c r="E13" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F13" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.02291666553439</v>
+        <v>2.928723958149338</v>
       </c>
       <c r="D14" t="n">
-        <v>17.00994961430926</v>
+        <v>2.764116812325256</v>
       </c>
       <c r="E14" t="n">
-        <v>6.159289169324181</v>
+        <v>1.000884490015179</v>
       </c>
       <c r="F14" t="n">
-        <v>16.05457057888841</v>
+        <v>2.608867719069366</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
